--- a/Gantt chart.xlsx
+++ b/Gantt chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Animish Murthy\Closet\Document\UVIC\25 summer semester\ECE 299\Clock-radio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001A6D6B-13EF-4632-B04E-13F690DE0395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B59085-D994-4A10-8936-BA928A7DE187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
   <si>
     <t xml:space="preserve">GANTT CHART </t>
   </si>
@@ -179,6 +179,9 @@
     <t>Project Initiation</t>
   </si>
   <si>
+    <t>Project Definition and Planning</t>
+  </si>
+  <si>
     <t>Scope and Goal Setting</t>
   </si>
   <si>
@@ -218,19 +221,25 @@
     <t>Chart Updates</t>
   </si>
   <si>
+    <t>Project Performance / Monitoring</t>
+  </si>
+  <si>
+    <t>Project Objectives</t>
+  </si>
+  <si>
+    <t>Quality Deliverables</t>
+  </si>
+  <si>
+    <t>Effort and Cost Tracking</t>
+  </si>
+  <si>
+    <t>Project Performance</t>
+  </si>
+  <si>
     <t>Clock-Radio</t>
   </si>
   <si>
     <t>MI6</t>
-  </si>
-  <si>
-    <t>OO7</t>
-  </si>
-  <si>
-    <t>Project Implementation</t>
-  </si>
-  <si>
-    <t>Project Testing &amp; Documentation</t>
   </si>
 </sst>
 </file>
@@ -286,7 +295,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -325,12 +333,10 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Century Gothic"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1001,44 +1007,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1046,6 +1014,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1056,6 +1028,40 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1402,7 @@
     <tabColor rgb="FF3D85C6"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BQ33"/>
+  <dimension ref="A1:BQ38"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.21875" customWidth="1"/>
@@ -1482,38 +1488,38 @@
     </row>
     <row r="2" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
       <c r="H2" s="10"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
       <c r="AF2" s="11"/>
       <c r="AG2" s="11"/>
       <c r="AH2" s="11"/>
@@ -1626,41 +1632,41 @@
     </row>
     <row r="4" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A4" s="1"/>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="86" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="82" t="s">
+      <c r="I4" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="99" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="81"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="81"/>
-      <c r="U4" s="81"/>
-      <c r="V4" s="81"/>
-      <c r="W4" s="81"/>
-      <c r="X4" s="81"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
-      <c r="AB4" s="81"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="85" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="82"/>
+      <c r="X4" s="82"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
+      <c r="AB4" s="82"/>
       <c r="AC4" s="17"/>
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
@@ -1705,40 +1711,40 @@
     </row>
     <row r="5" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A5" s="1"/>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="100">
+        <v>7</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="82" t="s">
+      <c r="I5" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="97">
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="83">
         <v>45850</v>
       </c>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="82"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="82"/>
       <c r="AB5" s="19"/>
       <c r="AC5" s="17"/>
       <c r="AD5" s="1"/>
@@ -1926,201 +1932,201 @@
     </row>
     <row r="8" spans="1:69" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="78" t="s">
+      <c r="C8" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="78" t="s">
+      <c r="D8" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="78" t="s">
+      <c r="H8" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="86" t="s">
+      <c r="I8" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="79"/>
-      <c r="N8" s="79"/>
-      <c r="O8" s="79"/>
-      <c r="P8" s="79"/>
-      <c r="Q8" s="79"/>
-      <c r="R8" s="79"/>
-      <c r="S8" s="79"/>
-      <c r="T8" s="79"/>
-      <c r="U8" s="79"/>
-      <c r="V8" s="79"/>
-      <c r="W8" s="79"/>
-      <c r="X8" s="92" t="s">
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="Y8" s="79"/>
-      <c r="Z8" s="79"/>
-      <c r="AA8" s="79"/>
-      <c r="AB8" s="79"/>
-      <c r="AC8" s="79"/>
-      <c r="AD8" s="79"/>
-      <c r="AE8" s="79"/>
-      <c r="AF8" s="79"/>
-      <c r="AG8" s="79"/>
-      <c r="AH8" s="79"/>
-      <c r="AI8" s="79"/>
-      <c r="AJ8" s="79"/>
-      <c r="AK8" s="79"/>
-      <c r="AL8" s="79"/>
-      <c r="AM8" s="91" t="s">
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AC8" s="88"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="88"/>
+      <c r="AG8" s="88"/>
+      <c r="AH8" s="88"/>
+      <c r="AI8" s="88"/>
+      <c r="AJ8" s="88"/>
+      <c r="AK8" s="88"/>
+      <c r="AL8" s="88"/>
+      <c r="AM8" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AN8" s="79"/>
-      <c r="AO8" s="79"/>
-      <c r="AP8" s="79"/>
-      <c r="AQ8" s="79"/>
-      <c r="AR8" s="79"/>
-      <c r="AS8" s="79"/>
-      <c r="AT8" s="79"/>
-      <c r="AU8" s="79"/>
-      <c r="AV8" s="79"/>
-      <c r="AW8" s="79"/>
-      <c r="AX8" s="79"/>
-      <c r="AY8" s="79"/>
-      <c r="AZ8" s="79"/>
-      <c r="BA8" s="79"/>
-      <c r="BB8" s="88" t="s">
+      <c r="AN8" s="88"/>
+      <c r="AO8" s="88"/>
+      <c r="AP8" s="88"/>
+      <c r="AQ8" s="88"/>
+      <c r="AR8" s="88"/>
+      <c r="AS8" s="88"/>
+      <c r="AT8" s="88"/>
+      <c r="AU8" s="88"/>
+      <c r="AV8" s="88"/>
+      <c r="AW8" s="88"/>
+      <c r="AX8" s="88"/>
+      <c r="AY8" s="88"/>
+      <c r="AZ8" s="88"/>
+      <c r="BA8" s="88"/>
+      <c r="BB8" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="BC8" s="79"/>
-      <c r="BD8" s="79"/>
-      <c r="BE8" s="79"/>
-      <c r="BF8" s="79"/>
-      <c r="BG8" s="79"/>
-      <c r="BH8" s="79"/>
-      <c r="BI8" s="79"/>
-      <c r="BJ8" s="79"/>
-      <c r="BK8" s="79"/>
-      <c r="BL8" s="79"/>
-      <c r="BM8" s="79"/>
-      <c r="BN8" s="79"/>
-      <c r="BO8" s="79"/>
-      <c r="BP8" s="89"/>
+      <c r="BC8" s="88"/>
+      <c r="BD8" s="88"/>
+      <c r="BE8" s="88"/>
+      <c r="BF8" s="88"/>
+      <c r="BG8" s="88"/>
+      <c r="BH8" s="88"/>
+      <c r="BI8" s="88"/>
+      <c r="BJ8" s="88"/>
+      <c r="BK8" s="88"/>
+      <c r="BL8" s="88"/>
+      <c r="BM8" s="88"/>
+      <c r="BN8" s="88"/>
+      <c r="BO8" s="88"/>
+      <c r="BP8" s="96"/>
       <c r="BQ8" s="21"/>
     </row>
     <row r="9" spans="1:69" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="83" t="s">
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="83" t="s">
+      <c r="J9" s="91"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="91"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="85"/>
-      <c r="S9" s="83" t="s">
+      <c r="O9" s="91"/>
+      <c r="P9" s="91"/>
+      <c r="Q9" s="91"/>
+      <c r="R9" s="92"/>
+      <c r="S9" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="84"/>
-      <c r="W9" s="85"/>
-      <c r="X9" s="93" t="s">
+      <c r="T9" s="91"/>
+      <c r="U9" s="91"/>
+      <c r="V9" s="91"/>
+      <c r="W9" s="92"/>
+      <c r="X9" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="85"/>
-      <c r="AC9" s="93" t="s">
+      <c r="Y9" s="91"/>
+      <c r="Z9" s="91"/>
+      <c r="AA9" s="91"/>
+      <c r="AB9" s="92"/>
+      <c r="AC9" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="AD9" s="84"/>
-      <c r="AE9" s="84"/>
-      <c r="AF9" s="84"/>
-      <c r="AG9" s="85"/>
-      <c r="AH9" s="93" t="s">
+      <c r="AD9" s="91"/>
+      <c r="AE9" s="91"/>
+      <c r="AF9" s="91"/>
+      <c r="AG9" s="92"/>
+      <c r="AH9" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="AI9" s="84"/>
-      <c r="AJ9" s="84"/>
-      <c r="AK9" s="84"/>
-      <c r="AL9" s="85"/>
-      <c r="AM9" s="90" t="s">
+      <c r="AI9" s="91"/>
+      <c r="AJ9" s="91"/>
+      <c r="AK9" s="91"/>
+      <c r="AL9" s="92"/>
+      <c r="AM9" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="AN9" s="84"/>
-      <c r="AO9" s="84"/>
-      <c r="AP9" s="84"/>
-      <c r="AQ9" s="85"/>
-      <c r="AR9" s="90" t="s">
+      <c r="AN9" s="91"/>
+      <c r="AO9" s="91"/>
+      <c r="AP9" s="91"/>
+      <c r="AQ9" s="92"/>
+      <c r="AR9" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="AS9" s="84"/>
-      <c r="AT9" s="84"/>
-      <c r="AU9" s="84"/>
-      <c r="AV9" s="85"/>
-      <c r="AW9" s="90" t="s">
+      <c r="AS9" s="91"/>
+      <c r="AT9" s="91"/>
+      <c r="AU9" s="91"/>
+      <c r="AV9" s="92"/>
+      <c r="AW9" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="AX9" s="84"/>
-      <c r="AY9" s="84"/>
-      <c r="AZ9" s="84"/>
-      <c r="BA9" s="85"/>
-      <c r="BB9" s="87" t="s">
+      <c r="AX9" s="91"/>
+      <c r="AY9" s="91"/>
+      <c r="AZ9" s="91"/>
+      <c r="BA9" s="92"/>
+      <c r="BB9" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="BC9" s="84"/>
-      <c r="BD9" s="84"/>
-      <c r="BE9" s="84"/>
-      <c r="BF9" s="85"/>
-      <c r="BG9" s="87" t="s">
+      <c r="BC9" s="91"/>
+      <c r="BD9" s="91"/>
+      <c r="BE9" s="91"/>
+      <c r="BF9" s="92"/>
+      <c r="BG9" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="BH9" s="84"/>
-      <c r="BI9" s="84"/>
-      <c r="BJ9" s="84"/>
-      <c r="BK9" s="85"/>
-      <c r="BL9" s="87" t="s">
+      <c r="BH9" s="91"/>
+      <c r="BI9" s="91"/>
+      <c r="BJ9" s="91"/>
+      <c r="BK9" s="92"/>
+      <c r="BL9" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BM9" s="84"/>
-      <c r="BN9" s="84"/>
-      <c r="BO9" s="84"/>
-      <c r="BP9" s="85"/>
+      <c r="BM9" s="91"/>
+      <c r="BN9" s="91"/>
+      <c r="BO9" s="91"/>
+      <c r="BP9" s="92"/>
       <c r="BQ9" s="25"/>
     </row>
     <row r="10" spans="1:69" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
       <c r="I10" s="27" t="s">
         <v>28</v>
       </c>
@@ -2986,7 +2992,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33"/>
@@ -3061,7 +3067,7 @@
         <v>2.1</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>42</v>
@@ -3146,7 +3152,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="39" t="s">
         <v>44</v>
@@ -3231,7 +3237,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>46</v>
@@ -3312,7 +3318,7 @@
         <v>2.4</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" s="39" t="s">
         <v>46</v>
@@ -3393,7 +3399,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
@@ -3468,7 +3474,7 @@
         <v>3.1</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" s="39" t="s">
         <v>40</v>
@@ -3549,7 +3555,7 @@
         <v>3.2</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>35</v>
@@ -3627,10 +3633,10 @@
     <row r="27" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" s="39" t="s">
         <v>38</v>
@@ -3708,10 +3714,10 @@
     <row r="28" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" s="38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>38</v>
@@ -3792,7 +3798,7 @@
         <v>3.3</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" s="39" t="s">
         <v>40</v>
@@ -3870,10 +3876,10 @@
     <row r="30" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D30" s="39" t="s">
         <v>46</v>
@@ -3950,219 +3956,643 @@
     </row>
     <row r="31" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="21"/>
-      <c r="X31" s="21"/>
-      <c r="Y31" s="21"/>
-      <c r="Z31" s="21"/>
-      <c r="AA31" s="21"/>
-      <c r="AB31" s="21"/>
-      <c r="AC31" s="21"/>
-      <c r="AD31" s="21"/>
-      <c r="AE31" s="21"/>
-      <c r="AF31" s="21"/>
-      <c r="AG31" s="21"/>
-      <c r="AH31" s="21"/>
-      <c r="AI31" s="21"/>
-      <c r="AJ31" s="21"/>
-      <c r="AK31" s="21"/>
-      <c r="AL31" s="21"/>
-      <c r="AM31" s="21"/>
-      <c r="AN31" s="21"/>
-      <c r="AO31" s="21"/>
-      <c r="AP31" s="21"/>
-      <c r="AQ31" s="21"/>
-      <c r="AR31" s="21"/>
-      <c r="AS31" s="21"/>
-      <c r="AT31" s="21"/>
-      <c r="AU31" s="21"/>
-      <c r="AV31" s="21"/>
-      <c r="AW31" s="21"/>
-      <c r="AX31" s="21"/>
-      <c r="AY31" s="21"/>
-      <c r="AZ31" s="21"/>
-      <c r="BA31" s="21"/>
-      <c r="BB31" s="21"/>
-      <c r="BC31" s="21"/>
-      <c r="BD31" s="21"/>
-      <c r="BE31" s="21"/>
-      <c r="BF31" s="21"/>
-      <c r="BG31" s="21"/>
-      <c r="BH31" s="21"/>
-      <c r="BI31" s="21"/>
-      <c r="BJ31" s="21"/>
-      <c r="BK31" s="21"/>
-      <c r="BL31" s="21"/>
-      <c r="BM31" s="21"/>
-      <c r="BN31" s="21"/>
-      <c r="BO31" s="21"/>
-      <c r="BP31" s="21"/>
+      <c r="B31" s="31">
+        <v>4</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="X31" s="34"/>
+      <c r="Y31" s="34"/>
+      <c r="Z31" s="34"/>
+      <c r="AA31" s="34"/>
+      <c r="AB31" s="34"/>
+      <c r="AC31" s="34"/>
+      <c r="AD31" s="34"/>
+      <c r="AE31" s="34"/>
+      <c r="AF31" s="34"/>
+      <c r="AG31" s="34"/>
+      <c r="AH31" s="34"/>
+      <c r="AI31" s="34"/>
+      <c r="AJ31" s="34"/>
+      <c r="AK31" s="34"/>
+      <c r="AL31" s="34"/>
+      <c r="AM31" s="34"/>
+      <c r="AN31" s="34"/>
+      <c r="AO31" s="34"/>
+      <c r="AP31" s="34"/>
+      <c r="AQ31" s="34"/>
+      <c r="AR31" s="34"/>
+      <c r="AS31" s="34"/>
+      <c r="AT31" s="34"/>
+      <c r="AU31" s="34"/>
+      <c r="AV31" s="34"/>
+      <c r="AW31" s="34"/>
+      <c r="AX31" s="34"/>
+      <c r="AY31" s="34"/>
+      <c r="AZ31" s="34"/>
+      <c r="BA31" s="34"/>
+      <c r="BB31" s="34"/>
+      <c r="BC31" s="34"/>
+      <c r="BD31" s="34"/>
+      <c r="BE31" s="34"/>
+      <c r="BF31" s="34"/>
+      <c r="BG31" s="34"/>
+      <c r="BH31" s="34"/>
+      <c r="BI31" s="34"/>
+      <c r="BJ31" s="34"/>
+      <c r="BK31" s="34"/>
+      <c r="BL31" s="34"/>
+      <c r="BM31" s="34"/>
+      <c r="BN31" s="34"/>
+      <c r="BO31" s="34"/>
+      <c r="BP31" s="34"/>
       <c r="BQ31" s="21"/>
     </row>
-    <row r="32" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
-      <c r="V32" s="21"/>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
-      <c r="Y32" s="21"/>
-      <c r="Z32" s="21"/>
-      <c r="AA32" s="21"/>
-      <c r="AB32" s="21"/>
-      <c r="AC32" s="21"/>
-      <c r="AD32" s="21"/>
-      <c r="AE32" s="21"/>
-      <c r="AF32" s="21"/>
-      <c r="AG32" s="21"/>
-      <c r="AH32" s="21"/>
-      <c r="AI32" s="21"/>
-      <c r="AJ32" s="21"/>
-      <c r="AK32" s="21"/>
-      <c r="AL32" s="21"/>
-      <c r="AM32" s="21"/>
-      <c r="AN32" s="21"/>
-      <c r="AO32" s="21"/>
-      <c r="AP32" s="21"/>
-      <c r="AQ32" s="21"/>
-      <c r="AR32" s="21"/>
-      <c r="AS32" s="21"/>
-      <c r="AT32" s="21"/>
-      <c r="AU32" s="21"/>
-      <c r="AV32" s="21"/>
-      <c r="AW32" s="21"/>
-      <c r="AX32" s="21"/>
-      <c r="AY32" s="21"/>
-      <c r="AZ32" s="21"/>
-      <c r="BA32" s="21"/>
-      <c r="BB32" s="21"/>
-      <c r="BC32" s="21"/>
-      <c r="BD32" s="21"/>
-      <c r="BE32" s="21"/>
-      <c r="BF32" s="21"/>
-      <c r="BG32" s="21"/>
-      <c r="BH32" s="21"/>
-      <c r="BI32" s="21"/>
-      <c r="BJ32" s="21"/>
-      <c r="BK32" s="21"/>
-      <c r="BL32" s="21"/>
-      <c r="BM32" s="21"/>
-      <c r="BN32" s="21"/>
-      <c r="BO32" s="21"/>
-      <c r="BP32" s="21"/>
-      <c r="BQ32" s="21"/>
+    <row r="32" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41">
+        <v>0</v>
+      </c>
+      <c r="H32" s="42">
+        <v>0</v>
+      </c>
+      <c r="I32" s="43"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="47"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="47"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="45"/>
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45"/>
+      <c r="Y32" s="45"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="48"/>
+      <c r="AD32" s="48"/>
+      <c r="AE32" s="48"/>
+      <c r="AF32" s="48"/>
+      <c r="AG32" s="48"/>
+      <c r="AH32" s="45"/>
+      <c r="AI32" s="45"/>
+      <c r="AJ32" s="45"/>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
+      <c r="AM32" s="45"/>
+      <c r="AN32" s="45"/>
+      <c r="AO32" s="45"/>
+      <c r="AP32" s="45"/>
+      <c r="AQ32" s="45"/>
+      <c r="AR32" s="49"/>
+      <c r="AS32" s="49"/>
+      <c r="AT32" s="49"/>
+      <c r="AU32" s="49"/>
+      <c r="AV32" s="49"/>
+      <c r="AW32" s="45"/>
+      <c r="AX32" s="45"/>
+      <c r="AY32" s="45"/>
+      <c r="AZ32" s="45"/>
+      <c r="BA32" s="45"/>
+      <c r="BB32" s="45"/>
+      <c r="BC32" s="45"/>
+      <c r="BD32" s="45"/>
+      <c r="BE32" s="45"/>
+      <c r="BF32" s="45"/>
+      <c r="BG32" s="50"/>
+      <c r="BH32" s="50"/>
+      <c r="BI32" s="50"/>
+      <c r="BJ32" s="50"/>
+      <c r="BK32" s="50"/>
+      <c r="BL32" s="45"/>
+      <c r="BM32" s="45"/>
+      <c r="BN32" s="45"/>
+      <c r="BO32" s="45"/>
+      <c r="BP32" s="51"/>
+      <c r="BQ32" s="37"/>
     </row>
-    <row r="33" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="21"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
-      <c r="AE33" s="21"/>
-      <c r="AF33" s="21"/>
-      <c r="AG33" s="21"/>
-      <c r="AH33" s="21"/>
-      <c r="AI33" s="21"/>
-      <c r="AJ33" s="21"/>
-      <c r="AK33" s="21"/>
-      <c r="AL33" s="21"/>
-      <c r="AM33" s="21"/>
-      <c r="AN33" s="21"/>
-      <c r="AO33" s="21"/>
-      <c r="AP33" s="21"/>
-      <c r="AQ33" s="21"/>
-      <c r="AR33" s="21"/>
-      <c r="AS33" s="21"/>
-      <c r="AT33" s="21"/>
-      <c r="AU33" s="21"/>
-      <c r="AV33" s="21"/>
-      <c r="AW33" s="21"/>
-      <c r="AX33" s="21"/>
-      <c r="AY33" s="21"/>
-      <c r="AZ33" s="21"/>
-      <c r="BA33" s="21"/>
-      <c r="BB33" s="21"/>
-      <c r="BC33" s="21"/>
-      <c r="BD33" s="21"/>
-      <c r="BE33" s="21"/>
-      <c r="BF33" s="21"/>
-      <c r="BG33" s="21"/>
-      <c r="BH33" s="21"/>
-      <c r="BI33" s="21"/>
-      <c r="BJ33" s="21"/>
-      <c r="BK33" s="21"/>
-      <c r="BL33" s="21"/>
-      <c r="BM33" s="21"/>
-      <c r="BN33" s="21"/>
-      <c r="BO33" s="21"/>
-      <c r="BP33" s="21"/>
-      <c r="BQ33" s="21"/>
+    <row r="33" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41">
+        <v>0</v>
+      </c>
+      <c r="H33" s="42">
+        <v>0</v>
+      </c>
+      <c r="I33" s="52"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="47"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="47"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47"/>
+      <c r="S33" s="54"/>
+      <c r="T33" s="54"/>
+      <c r="U33" s="54"/>
+      <c r="V33" s="54"/>
+      <c r="W33" s="54"/>
+      <c r="X33" s="54"/>
+      <c r="Y33" s="54"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="54"/>
+      <c r="AB33" s="54"/>
+      <c r="AC33" s="57"/>
+      <c r="AD33" s="57"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="57"/>
+      <c r="AH33" s="54"/>
+      <c r="AI33" s="54"/>
+      <c r="AJ33" s="54"/>
+      <c r="AK33" s="54"/>
+      <c r="AL33" s="54"/>
+      <c r="AM33" s="54"/>
+      <c r="AN33" s="54"/>
+      <c r="AO33" s="54"/>
+      <c r="AP33" s="54"/>
+      <c r="AQ33" s="54"/>
+      <c r="AR33" s="58"/>
+      <c r="AS33" s="58"/>
+      <c r="AT33" s="58"/>
+      <c r="AU33" s="58"/>
+      <c r="AV33" s="58"/>
+      <c r="AW33" s="54"/>
+      <c r="AX33" s="54"/>
+      <c r="AY33" s="54"/>
+      <c r="AZ33" s="54"/>
+      <c r="BA33" s="54"/>
+      <c r="BB33" s="54"/>
+      <c r="BC33" s="54"/>
+      <c r="BD33" s="54"/>
+      <c r="BE33" s="54"/>
+      <c r="BF33" s="54"/>
+      <c r="BG33" s="59"/>
+      <c r="BH33" s="59"/>
+      <c r="BI33" s="59"/>
+      <c r="BJ33" s="59"/>
+      <c r="BK33" s="59"/>
+      <c r="BL33" s="54"/>
+      <c r="BM33" s="54"/>
+      <c r="BN33" s="54"/>
+      <c r="BO33" s="54"/>
+      <c r="BP33" s="60"/>
+      <c r="BQ33" s="37"/>
+    </row>
+    <row r="34" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38">
+        <v>4.3</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="41">
+        <v>0</v>
+      </c>
+      <c r="H34" s="42">
+        <v>0</v>
+      </c>
+      <c r="I34" s="52"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="54"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="45"/>
+      <c r="U34" s="45"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="54"/>
+      <c r="X34" s="54"/>
+      <c r="Y34" s="54"/>
+      <c r="Z34" s="54"/>
+      <c r="AA34" s="54"/>
+      <c r="AB34" s="54"/>
+      <c r="AC34" s="57"/>
+      <c r="AD34" s="57"/>
+      <c r="AE34" s="57"/>
+      <c r="AF34" s="57"/>
+      <c r="AG34" s="57"/>
+      <c r="AH34" s="54"/>
+      <c r="AI34" s="54"/>
+      <c r="AJ34" s="54"/>
+      <c r="AK34" s="54"/>
+      <c r="AL34" s="54"/>
+      <c r="AM34" s="54"/>
+      <c r="AN34" s="54"/>
+      <c r="AO34" s="54"/>
+      <c r="AP34" s="54"/>
+      <c r="AQ34" s="54"/>
+      <c r="AR34" s="58"/>
+      <c r="AS34" s="58"/>
+      <c r="AT34" s="58"/>
+      <c r="AU34" s="58"/>
+      <c r="AV34" s="58"/>
+      <c r="AW34" s="54"/>
+      <c r="AX34" s="54"/>
+      <c r="AY34" s="54"/>
+      <c r="AZ34" s="54"/>
+      <c r="BA34" s="54"/>
+      <c r="BB34" s="54"/>
+      <c r="BC34" s="54"/>
+      <c r="BD34" s="54"/>
+      <c r="BE34" s="54"/>
+      <c r="BF34" s="54"/>
+      <c r="BG34" s="59"/>
+      <c r="BH34" s="59"/>
+      <c r="BI34" s="59"/>
+      <c r="BJ34" s="59"/>
+      <c r="BK34" s="59"/>
+      <c r="BL34" s="54"/>
+      <c r="BM34" s="54"/>
+      <c r="BN34" s="54"/>
+      <c r="BO34" s="54"/>
+      <c r="BP34" s="60"/>
+      <c r="BQ34" s="37"/>
+    </row>
+    <row r="35" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="37"/>
+      <c r="B35" s="38">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="41">
+        <v>0</v>
+      </c>
+      <c r="H35" s="61">
+        <v>0</v>
+      </c>
+      <c r="I35" s="52"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47"/>
+      <c r="S35" s="45"/>
+      <c r="T35" s="45"/>
+      <c r="U35" s="45"/>
+      <c r="V35" s="45"/>
+      <c r="W35" s="54"/>
+      <c r="X35" s="54"/>
+      <c r="Y35" s="54"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="54"/>
+      <c r="AB35" s="54"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="57"/>
+      <c r="AH35" s="54"/>
+      <c r="AI35" s="54"/>
+      <c r="AJ35" s="54"/>
+      <c r="AK35" s="54"/>
+      <c r="AL35" s="54"/>
+      <c r="AM35" s="54"/>
+      <c r="AN35" s="54"/>
+      <c r="AO35" s="54"/>
+      <c r="AP35" s="54"/>
+      <c r="AQ35" s="54"/>
+      <c r="AR35" s="58"/>
+      <c r="AS35" s="58"/>
+      <c r="AT35" s="58"/>
+      <c r="AU35" s="58"/>
+      <c r="AV35" s="58"/>
+      <c r="AW35" s="54"/>
+      <c r="AX35" s="54"/>
+      <c r="AY35" s="54"/>
+      <c r="AZ35" s="54"/>
+      <c r="BA35" s="54"/>
+      <c r="BB35" s="54"/>
+      <c r="BC35" s="54"/>
+      <c r="BD35" s="54"/>
+      <c r="BE35" s="54"/>
+      <c r="BF35" s="54"/>
+      <c r="BG35" s="59"/>
+      <c r="BH35" s="59"/>
+      <c r="BI35" s="59"/>
+      <c r="BJ35" s="59"/>
+      <c r="BK35" s="59"/>
+      <c r="BL35" s="54"/>
+      <c r="BM35" s="54"/>
+      <c r="BN35" s="54"/>
+      <c r="BO35" s="54"/>
+      <c r="BP35" s="60"/>
+      <c r="BQ35" s="37"/>
+    </row>
+    <row r="36" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
+      <c r="R36" s="21"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="21"/>
+      <c r="V36" s="21"/>
+      <c r="W36" s="21"/>
+      <c r="X36" s="21"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
+      <c r="AA36" s="21"/>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="21"/>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+      <c r="AG36" s="21"/>
+      <c r="AH36" s="21"/>
+      <c r="AI36" s="21"/>
+      <c r="AJ36" s="21"/>
+      <c r="AK36" s="21"/>
+      <c r="AL36" s="21"/>
+      <c r="AM36" s="21"/>
+      <c r="AN36" s="21"/>
+      <c r="AO36" s="21"/>
+      <c r="AP36" s="21"/>
+      <c r="AQ36" s="21"/>
+      <c r="AR36" s="21"/>
+      <c r="AS36" s="21"/>
+      <c r="AT36" s="21"/>
+      <c r="AU36" s="21"/>
+      <c r="AV36" s="21"/>
+      <c r="AW36" s="21"/>
+      <c r="AX36" s="21"/>
+      <c r="AY36" s="21"/>
+      <c r="AZ36" s="21"/>
+      <c r="BA36" s="21"/>
+      <c r="BB36" s="21"/>
+      <c r="BC36" s="21"/>
+      <c r="BD36" s="21"/>
+      <c r="BE36" s="21"/>
+      <c r="BF36" s="21"/>
+      <c r="BG36" s="21"/>
+      <c r="BH36" s="21"/>
+      <c r="BI36" s="21"/>
+      <c r="BJ36" s="21"/>
+      <c r="BK36" s="21"/>
+      <c r="BL36" s="21"/>
+      <c r="BM36" s="21"/>
+      <c r="BN36" s="21"/>
+      <c r="BO36" s="21"/>
+      <c r="BP36" s="21"/>
+      <c r="BQ36" s="21"/>
+    </row>
+    <row r="37" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="21"/>
+      <c r="R37" s="21"/>
+      <c r="S37" s="21"/>
+      <c r="T37" s="21"/>
+      <c r="U37" s="21"/>
+      <c r="V37" s="21"/>
+      <c r="W37" s="21"/>
+      <c r="X37" s="21"/>
+      <c r="Y37" s="21"/>
+      <c r="Z37" s="21"/>
+      <c r="AA37" s="21"/>
+      <c r="AB37" s="21"/>
+      <c r="AC37" s="21"/>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
+      <c r="AF37" s="21"/>
+      <c r="AG37" s="21"/>
+      <c r="AH37" s="21"/>
+      <c r="AI37" s="21"/>
+      <c r="AJ37" s="21"/>
+      <c r="AK37" s="21"/>
+      <c r="AL37" s="21"/>
+      <c r="AM37" s="21"/>
+      <c r="AN37" s="21"/>
+      <c r="AO37" s="21"/>
+      <c r="AP37" s="21"/>
+      <c r="AQ37" s="21"/>
+      <c r="AR37" s="21"/>
+      <c r="AS37" s="21"/>
+      <c r="AT37" s="21"/>
+      <c r="AU37" s="21"/>
+      <c r="AV37" s="21"/>
+      <c r="AW37" s="21"/>
+      <c r="AX37" s="21"/>
+      <c r="AY37" s="21"/>
+      <c r="AZ37" s="21"/>
+      <c r="BA37" s="21"/>
+      <c r="BB37" s="21"/>
+      <c r="BC37" s="21"/>
+      <c r="BD37" s="21"/>
+      <c r="BE37" s="21"/>
+      <c r="BF37" s="21"/>
+      <c r="BG37" s="21"/>
+      <c r="BH37" s="21"/>
+      <c r="BI37" s="21"/>
+      <c r="BJ37" s="21"/>
+      <c r="BK37" s="21"/>
+      <c r="BL37" s="21"/>
+      <c r="BM37" s="21"/>
+      <c r="BN37" s="21"/>
+      <c r="BO37" s="21"/>
+      <c r="BP37" s="21"/>
+      <c r="BQ37" s="21"/>
+    </row>
+    <row r="38" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
+      <c r="R38" s="21"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="21"/>
+      <c r="U38" s="21"/>
+      <c r="V38" s="21"/>
+      <c r="W38" s="21"/>
+      <c r="X38" s="21"/>
+      <c r="Y38" s="21"/>
+      <c r="Z38" s="21"/>
+      <c r="AA38" s="21"/>
+      <c r="AB38" s="21"/>
+      <c r="AC38" s="21"/>
+      <c r="AD38" s="21"/>
+      <c r="AE38" s="21"/>
+      <c r="AF38" s="21"/>
+      <c r="AG38" s="21"/>
+      <c r="AH38" s="21"/>
+      <c r="AI38" s="21"/>
+      <c r="AJ38" s="21"/>
+      <c r="AK38" s="21"/>
+      <c r="AL38" s="21"/>
+      <c r="AM38" s="21"/>
+      <c r="AN38" s="21"/>
+      <c r="AO38" s="21"/>
+      <c r="AP38" s="21"/>
+      <c r="AQ38" s="21"/>
+      <c r="AR38" s="21"/>
+      <c r="AS38" s="21"/>
+      <c r="AT38" s="21"/>
+      <c r="AU38" s="21"/>
+      <c r="AV38" s="21"/>
+      <c r="AW38" s="21"/>
+      <c r="AX38" s="21"/>
+      <c r="AY38" s="21"/>
+      <c r="AZ38" s="21"/>
+      <c r="BA38" s="21"/>
+      <c r="BB38" s="21"/>
+      <c r="BC38" s="21"/>
+      <c r="BD38" s="21"/>
+      <c r="BE38" s="21"/>
+      <c r="BF38" s="21"/>
+      <c r="BG38" s="21"/>
+      <c r="BH38" s="21"/>
+      <c r="BI38" s="21"/>
+      <c r="BJ38" s="21"/>
+      <c r="BK38" s="21"/>
+      <c r="BL38" s="21"/>
+      <c r="BM38" s="21"/>
+      <c r="BN38" s="21"/>
+      <c r="BO38" s="21"/>
+      <c r="BP38" s="21"/>
+      <c r="BQ38" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="N9:R9"/>
+    <mergeCell ref="I9:M9"/>
+    <mergeCell ref="I8:W8"/>
+    <mergeCell ref="BG9:BK9"/>
+    <mergeCell ref="BL9:BP9"/>
+    <mergeCell ref="BB9:BF9"/>
+    <mergeCell ref="BB8:BP8"/>
+    <mergeCell ref="AM9:AQ9"/>
+    <mergeCell ref="AM8:BA8"/>
+    <mergeCell ref="X8:AL8"/>
+    <mergeCell ref="X9:AB9"/>
+    <mergeCell ref="AH9:AL9"/>
+    <mergeCell ref="AC9:AG9"/>
+    <mergeCell ref="AR9:AV9"/>
+    <mergeCell ref="AW9:BA9"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I5:O5"/>
@@ -4172,34 +4602,9 @@
     <mergeCell ref="P4:AB4"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="BL9:BP9"/>
-    <mergeCell ref="BB9:BF9"/>
-    <mergeCell ref="BB8:BP8"/>
-    <mergeCell ref="AM9:AQ9"/>
-    <mergeCell ref="AM8:BA8"/>
-    <mergeCell ref="AR9:AV9"/>
-    <mergeCell ref="AW9:BA9"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="N9:R9"/>
-    <mergeCell ref="I9:M9"/>
-    <mergeCell ref="I8:W8"/>
-    <mergeCell ref="BG9:BK9"/>
-    <mergeCell ref="X8:AL8"/>
-    <mergeCell ref="X9:AB9"/>
-    <mergeCell ref="AH9:AL9"/>
-    <mergeCell ref="AC9:AG9"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
   </mergeCells>
-  <conditionalFormatting sqref="H12:H18 H20:H30">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="H12:H18 H20:H35">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4207,7 +4612,7 @@
         <color rgb="FF57BB8A"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>

--- a/Gantt chart.xlsx
+++ b/Gantt chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Animish Murthy\Closet\Document\UVIC\25 summer semester\ECE 299\Clock-radio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B59085-D994-4A10-8936-BA928A7DE187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001A6D6B-13EF-4632-B04E-13F690DE0395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t xml:space="preserve">GANTT CHART </t>
   </si>
@@ -179,9 +179,6 @@
     <t>Project Initiation</t>
   </si>
   <si>
-    <t>Project Definition and Planning</t>
-  </si>
-  <si>
     <t>Scope and Goal Setting</t>
   </si>
   <si>
@@ -221,25 +218,19 @@
     <t>Chart Updates</t>
   </si>
   <si>
-    <t>Project Performance / Monitoring</t>
-  </si>
-  <si>
-    <t>Project Objectives</t>
-  </si>
-  <si>
-    <t>Quality Deliverables</t>
-  </si>
-  <si>
-    <t>Effort and Cost Tracking</t>
-  </si>
-  <si>
-    <t>Project Performance</t>
-  </si>
-  <si>
     <t>Clock-Radio</t>
   </si>
   <si>
     <t>MI6</t>
+  </si>
+  <si>
+    <t>OO7</t>
+  </si>
+  <si>
+    <t>Project Implementation</t>
+  </si>
+  <si>
+    <t>Project Testing &amp; Documentation</t>
   </si>
 </sst>
 </file>
@@ -295,6 +286,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -333,10 +325,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Century Gothic"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1007,6 +1001,44 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1014,10 +1046,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1028,40 +1056,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1402,7 +1396,7 @@
     <tabColor rgb="FF3D85C6"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BQ38"/>
+  <dimension ref="A1:BQ33"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.21875" customWidth="1"/>
@@ -1488,38 +1482,38 @@
     </row>
     <row r="2" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
       <c r="H2" s="10"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="79"/>
-      <c r="AE2" s="79"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="95"/>
+      <c r="T2" s="95"/>
+      <c r="U2" s="95"/>
+      <c r="V2" s="95"/>
+      <c r="W2" s="95"/>
+      <c r="X2" s="95"/>
+      <c r="Y2" s="95"/>
+      <c r="Z2" s="95"/>
+      <c r="AA2" s="95"/>
+      <c r="AB2" s="95"/>
+      <c r="AC2" s="95"/>
+      <c r="AD2" s="95"/>
+      <c r="AE2" s="95"/>
       <c r="AF2" s="11"/>
       <c r="AG2" s="11"/>
       <c r="AH2" s="11"/>
@@ -1632,41 +1626,41 @@
     </row>
     <row r="4" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A4" s="1"/>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="86" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="81" t="s">
+      <c r="I4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="85" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="82"/>
-      <c r="W4" s="82"/>
-      <c r="X4" s="82"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="99" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="81"/>
       <c r="AC4" s="17"/>
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
@@ -1711,40 +1705,40 @@
     </row>
     <row r="5" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A5" s="1"/>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="100">
-        <v>7</v>
-      </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="81" t="s">
+      <c r="I5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="83">
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="97">
         <v>45850</v>
       </c>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="82"/>
-      <c r="Y5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="81"/>
+      <c r="AA5" s="81"/>
       <c r="AB5" s="19"/>
       <c r="AC5" s="17"/>
       <c r="AD5" s="1"/>
@@ -1932,201 +1926,201 @@
     </row>
     <row r="8" spans="1:69" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="97" t="s">
+      <c r="D8" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="97" t="s">
+      <c r="F8" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="97" t="s">
+      <c r="G8" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="97" t="s">
+      <c r="H8" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="99" t="s">
+      <c r="I8" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="88"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="88"/>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="89" t="s">
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="79"/>
+      <c r="R8" s="79"/>
+      <c r="S8" s="79"/>
+      <c r="T8" s="79"/>
+      <c r="U8" s="79"/>
+      <c r="V8" s="79"/>
+      <c r="W8" s="79"/>
+      <c r="X8" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="Y8" s="88"/>
-      <c r="Z8" s="88"/>
-      <c r="AA8" s="88"/>
-      <c r="AB8" s="88"/>
-      <c r="AC8" s="88"/>
-      <c r="AD8" s="88"/>
-      <c r="AE8" s="88"/>
-      <c r="AF8" s="88"/>
-      <c r="AG8" s="88"/>
-      <c r="AH8" s="88"/>
-      <c r="AI8" s="88"/>
-      <c r="AJ8" s="88"/>
-      <c r="AK8" s="88"/>
-      <c r="AL8" s="88"/>
-      <c r="AM8" s="87" t="s">
+      <c r="Y8" s="79"/>
+      <c r="Z8" s="79"/>
+      <c r="AA8" s="79"/>
+      <c r="AB8" s="79"/>
+      <c r="AC8" s="79"/>
+      <c r="AD8" s="79"/>
+      <c r="AE8" s="79"/>
+      <c r="AF8" s="79"/>
+      <c r="AG8" s="79"/>
+      <c r="AH8" s="79"/>
+      <c r="AI8" s="79"/>
+      <c r="AJ8" s="79"/>
+      <c r="AK8" s="79"/>
+      <c r="AL8" s="79"/>
+      <c r="AM8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="AN8" s="88"/>
-      <c r="AO8" s="88"/>
-      <c r="AP8" s="88"/>
-      <c r="AQ8" s="88"/>
-      <c r="AR8" s="88"/>
-      <c r="AS8" s="88"/>
-      <c r="AT8" s="88"/>
-      <c r="AU8" s="88"/>
-      <c r="AV8" s="88"/>
-      <c r="AW8" s="88"/>
-      <c r="AX8" s="88"/>
-      <c r="AY8" s="88"/>
-      <c r="AZ8" s="88"/>
-      <c r="BA8" s="88"/>
-      <c r="BB8" s="95" t="s">
+      <c r="AN8" s="79"/>
+      <c r="AO8" s="79"/>
+      <c r="AP8" s="79"/>
+      <c r="AQ8" s="79"/>
+      <c r="AR8" s="79"/>
+      <c r="AS8" s="79"/>
+      <c r="AT8" s="79"/>
+      <c r="AU8" s="79"/>
+      <c r="AV8" s="79"/>
+      <c r="AW8" s="79"/>
+      <c r="AX8" s="79"/>
+      <c r="AY8" s="79"/>
+      <c r="AZ8" s="79"/>
+      <c r="BA8" s="79"/>
+      <c r="BB8" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="BC8" s="88"/>
-      <c r="BD8" s="88"/>
-      <c r="BE8" s="88"/>
-      <c r="BF8" s="88"/>
-      <c r="BG8" s="88"/>
-      <c r="BH8" s="88"/>
-      <c r="BI8" s="88"/>
-      <c r="BJ8" s="88"/>
-      <c r="BK8" s="88"/>
-      <c r="BL8" s="88"/>
-      <c r="BM8" s="88"/>
-      <c r="BN8" s="88"/>
-      <c r="BO8" s="88"/>
-      <c r="BP8" s="96"/>
+      <c r="BC8" s="79"/>
+      <c r="BD8" s="79"/>
+      <c r="BE8" s="79"/>
+      <c r="BF8" s="79"/>
+      <c r="BG8" s="79"/>
+      <c r="BH8" s="79"/>
+      <c r="BI8" s="79"/>
+      <c r="BJ8" s="79"/>
+      <c r="BK8" s="79"/>
+      <c r="BL8" s="79"/>
+      <c r="BM8" s="79"/>
+      <c r="BN8" s="79"/>
+      <c r="BO8" s="79"/>
+      <c r="BP8" s="89"/>
       <c r="BQ8" s="21"/>
     </row>
     <row r="9" spans="1:69" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="98" t="s">
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="98" t="s">
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="91"/>
-      <c r="P9" s="91"/>
-      <c r="Q9" s="91"/>
-      <c r="R9" s="92"/>
-      <c r="S9" s="98" t="s">
+      <c r="O9" s="84"/>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="84"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="T9" s="91"/>
-      <c r="U9" s="91"/>
-      <c r="V9" s="91"/>
-      <c r="W9" s="92"/>
-      <c r="X9" s="90" t="s">
+      <c r="T9" s="84"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="84"/>
+      <c r="W9" s="85"/>
+      <c r="X9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="Y9" s="91"/>
-      <c r="Z9" s="91"/>
-      <c r="AA9" s="91"/>
-      <c r="AB9" s="92"/>
-      <c r="AC9" s="90" t="s">
+      <c r="Y9" s="84"/>
+      <c r="Z9" s="84"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="85"/>
+      <c r="AC9" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="AD9" s="91"/>
-      <c r="AE9" s="91"/>
-      <c r="AF9" s="91"/>
-      <c r="AG9" s="92"/>
-      <c r="AH9" s="90" t="s">
+      <c r="AD9" s="84"/>
+      <c r="AE9" s="84"/>
+      <c r="AF9" s="84"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="AI9" s="91"/>
-      <c r="AJ9" s="91"/>
-      <c r="AK9" s="91"/>
-      <c r="AL9" s="92"/>
-      <c r="AM9" s="93" t="s">
+      <c r="AI9" s="84"/>
+      <c r="AJ9" s="84"/>
+      <c r="AK9" s="84"/>
+      <c r="AL9" s="85"/>
+      <c r="AM9" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="AN9" s="91"/>
-      <c r="AO9" s="91"/>
-      <c r="AP9" s="91"/>
-      <c r="AQ9" s="92"/>
-      <c r="AR9" s="93" t="s">
+      <c r="AN9" s="84"/>
+      <c r="AO9" s="84"/>
+      <c r="AP9" s="84"/>
+      <c r="AQ9" s="85"/>
+      <c r="AR9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="AS9" s="91"/>
-      <c r="AT9" s="91"/>
-      <c r="AU9" s="91"/>
-      <c r="AV9" s="92"/>
-      <c r="AW9" s="93" t="s">
+      <c r="AS9" s="84"/>
+      <c r="AT9" s="84"/>
+      <c r="AU9" s="84"/>
+      <c r="AV9" s="85"/>
+      <c r="AW9" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="AX9" s="91"/>
-      <c r="AY9" s="91"/>
-      <c r="AZ9" s="91"/>
-      <c r="BA9" s="92"/>
-      <c r="BB9" s="94" t="s">
+      <c r="AX9" s="84"/>
+      <c r="AY9" s="84"/>
+      <c r="AZ9" s="84"/>
+      <c r="BA9" s="85"/>
+      <c r="BB9" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="BC9" s="91"/>
-      <c r="BD9" s="91"/>
-      <c r="BE9" s="91"/>
-      <c r="BF9" s="92"/>
-      <c r="BG9" s="94" t="s">
+      <c r="BC9" s="84"/>
+      <c r="BD9" s="84"/>
+      <c r="BE9" s="84"/>
+      <c r="BF9" s="85"/>
+      <c r="BG9" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="BH9" s="91"/>
-      <c r="BI9" s="91"/>
-      <c r="BJ9" s="91"/>
-      <c r="BK9" s="92"/>
-      <c r="BL9" s="94" t="s">
+      <c r="BH9" s="84"/>
+      <c r="BI9" s="84"/>
+      <c r="BJ9" s="84"/>
+      <c r="BK9" s="85"/>
+      <c r="BL9" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="BM9" s="91"/>
-      <c r="BN9" s="91"/>
-      <c r="BO9" s="91"/>
-      <c r="BP9" s="92"/>
+      <c r="BM9" s="84"/>
+      <c r="BN9" s="84"/>
+      <c r="BO9" s="84"/>
+      <c r="BP9" s="85"/>
       <c r="BQ9" s="25"/>
     </row>
     <row r="10" spans="1:69" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
       <c r="I10" s="27" t="s">
         <v>28</v>
       </c>
@@ -2992,7 +2986,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33"/>
@@ -3067,7 +3061,7 @@
         <v>2.1</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>42</v>
@@ -3152,7 +3146,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="39" t="s">
         <v>44</v>
@@ -3237,7 +3231,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>46</v>
@@ -3318,7 +3312,7 @@
         <v>2.4</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="39" t="s">
         <v>46</v>
@@ -3399,7 +3393,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
@@ -3474,7 +3468,7 @@
         <v>3.1</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="39" t="s">
         <v>40</v>
@@ -3555,7 +3549,7 @@
         <v>3.2</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>35</v>
@@ -3633,10 +3627,10 @@
     <row r="27" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="39" t="s">
         <v>55</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>56</v>
       </c>
       <c r="D27" s="39" t="s">
         <v>38</v>
@@ -3714,10 +3708,10 @@
     <row r="28" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="39" t="s">
         <v>57</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>58</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>38</v>
@@ -3798,7 +3792,7 @@
         <v>3.3</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" s="39" t="s">
         <v>40</v>
@@ -3876,10 +3870,10 @@
     <row r="30" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="39" t="s">
         <v>60</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>61</v>
       </c>
       <c r="D30" s="39" t="s">
         <v>46</v>
@@ -3956,618 +3950,244 @@
     </row>
     <row r="31" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
-      <c r="B31" s="31">
-        <v>4</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
-      <c r="AC31" s="34"/>
-      <c r="AD31" s="34"/>
-      <c r="AE31" s="34"/>
-      <c r="AF31" s="34"/>
-      <c r="AG31" s="34"/>
-      <c r="AH31" s="34"/>
-      <c r="AI31" s="34"/>
-      <c r="AJ31" s="34"/>
-      <c r="AK31" s="34"/>
-      <c r="AL31" s="34"/>
-      <c r="AM31" s="34"/>
-      <c r="AN31" s="34"/>
-      <c r="AO31" s="34"/>
-      <c r="AP31" s="34"/>
-      <c r="AQ31" s="34"/>
-      <c r="AR31" s="34"/>
-      <c r="AS31" s="34"/>
-      <c r="AT31" s="34"/>
-      <c r="AU31" s="34"/>
-      <c r="AV31" s="34"/>
-      <c r="AW31" s="34"/>
-      <c r="AX31" s="34"/>
-      <c r="AY31" s="34"/>
-      <c r="AZ31" s="34"/>
-      <c r="BA31" s="34"/>
-      <c r="BB31" s="34"/>
-      <c r="BC31" s="34"/>
-      <c r="BD31" s="34"/>
-      <c r="BE31" s="34"/>
-      <c r="BF31" s="34"/>
-      <c r="BG31" s="34"/>
-      <c r="BH31" s="34"/>
-      <c r="BI31" s="34"/>
-      <c r="BJ31" s="34"/>
-      <c r="BK31" s="34"/>
-      <c r="BL31" s="34"/>
-      <c r="BM31" s="34"/>
-      <c r="BN31" s="34"/>
-      <c r="BO31" s="34"/>
-      <c r="BP31" s="34"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+      <c r="V31" s="21"/>
+      <c r="W31" s="21"/>
+      <c r="X31" s="21"/>
+      <c r="Y31" s="21"/>
+      <c r="Z31" s="21"/>
+      <c r="AA31" s="21"/>
+      <c r="AB31" s="21"/>
+      <c r="AC31" s="21"/>
+      <c r="AD31" s="21"/>
+      <c r="AE31" s="21"/>
+      <c r="AF31" s="21"/>
+      <c r="AG31" s="21"/>
+      <c r="AH31" s="21"/>
+      <c r="AI31" s="21"/>
+      <c r="AJ31" s="21"/>
+      <c r="AK31" s="21"/>
+      <c r="AL31" s="21"/>
+      <c r="AM31" s="21"/>
+      <c r="AN31" s="21"/>
+      <c r="AO31" s="21"/>
+      <c r="AP31" s="21"/>
+      <c r="AQ31" s="21"/>
+      <c r="AR31" s="21"/>
+      <c r="AS31" s="21"/>
+      <c r="AT31" s="21"/>
+      <c r="AU31" s="21"/>
+      <c r="AV31" s="21"/>
+      <c r="AW31" s="21"/>
+      <c r="AX31" s="21"/>
+      <c r="AY31" s="21"/>
+      <c r="AZ31" s="21"/>
+      <c r="BA31" s="21"/>
+      <c r="BB31" s="21"/>
+      <c r="BC31" s="21"/>
+      <c r="BD31" s="21"/>
+      <c r="BE31" s="21"/>
+      <c r="BF31" s="21"/>
+      <c r="BG31" s="21"/>
+      <c r="BH31" s="21"/>
+      <c r="BI31" s="21"/>
+      <c r="BJ31" s="21"/>
+      <c r="BK31" s="21"/>
+      <c r="BL31" s="21"/>
+      <c r="BM31" s="21"/>
+      <c r="BN31" s="21"/>
+      <c r="BO31" s="21"/>
+      <c r="BP31" s="21"/>
       <c r="BQ31" s="21"/>
     </row>
-    <row r="32" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41">
-        <v>0</v>
-      </c>
-      <c r="H32" s="42">
-        <v>0</v>
-      </c>
-      <c r="I32" s="43"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="47"/>
-      <c r="O32" s="47"/>
-      <c r="P32" s="47"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45"/>
-      <c r="Y32" s="45"/>
-      <c r="Z32" s="45"/>
-      <c r="AA32" s="45"/>
-      <c r="AB32" s="45"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="48"/>
-      <c r="AF32" s="48"/>
-      <c r="AG32" s="48"/>
-      <c r="AH32" s="45"/>
-      <c r="AI32" s="45"/>
-      <c r="AJ32" s="45"/>
-      <c r="AK32" s="45"/>
-      <c r="AL32" s="45"/>
-      <c r="AM32" s="45"/>
-      <c r="AN32" s="45"/>
-      <c r="AO32" s="45"/>
-      <c r="AP32" s="45"/>
-      <c r="AQ32" s="45"/>
-      <c r="AR32" s="49"/>
-      <c r="AS32" s="49"/>
-      <c r="AT32" s="49"/>
-      <c r="AU32" s="49"/>
-      <c r="AV32" s="49"/>
-      <c r="AW32" s="45"/>
-      <c r="AX32" s="45"/>
-      <c r="AY32" s="45"/>
-      <c r="AZ32" s="45"/>
-      <c r="BA32" s="45"/>
-      <c r="BB32" s="45"/>
-      <c r="BC32" s="45"/>
-      <c r="BD32" s="45"/>
-      <c r="BE32" s="45"/>
-      <c r="BF32" s="45"/>
-      <c r="BG32" s="50"/>
-      <c r="BH32" s="50"/>
-      <c r="BI32" s="50"/>
-      <c r="BJ32" s="50"/>
-      <c r="BK32" s="50"/>
-      <c r="BL32" s="45"/>
-      <c r="BM32" s="45"/>
-      <c r="BN32" s="45"/>
-      <c r="BO32" s="45"/>
-      <c r="BP32" s="51"/>
-      <c r="BQ32" s="37"/>
+    <row r="32" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="21"/>
+      <c r="V32" s="21"/>
+      <c r="W32" s="21"/>
+      <c r="X32" s="21"/>
+      <c r="Y32" s="21"/>
+      <c r="Z32" s="21"/>
+      <c r="AA32" s="21"/>
+      <c r="AB32" s="21"/>
+      <c r="AC32" s="21"/>
+      <c r="AD32" s="21"/>
+      <c r="AE32" s="21"/>
+      <c r="AF32" s="21"/>
+      <c r="AG32" s="21"/>
+      <c r="AH32" s="21"/>
+      <c r="AI32" s="21"/>
+      <c r="AJ32" s="21"/>
+      <c r="AK32" s="21"/>
+      <c r="AL32" s="21"/>
+      <c r="AM32" s="21"/>
+      <c r="AN32" s="21"/>
+      <c r="AO32" s="21"/>
+      <c r="AP32" s="21"/>
+      <c r="AQ32" s="21"/>
+      <c r="AR32" s="21"/>
+      <c r="AS32" s="21"/>
+      <c r="AT32" s="21"/>
+      <c r="AU32" s="21"/>
+      <c r="AV32" s="21"/>
+      <c r="AW32" s="21"/>
+      <c r="AX32" s="21"/>
+      <c r="AY32" s="21"/>
+      <c r="AZ32" s="21"/>
+      <c r="BA32" s="21"/>
+      <c r="BB32" s="21"/>
+      <c r="BC32" s="21"/>
+      <c r="BD32" s="21"/>
+      <c r="BE32" s="21"/>
+      <c r="BF32" s="21"/>
+      <c r="BG32" s="21"/>
+      <c r="BH32" s="21"/>
+      <c r="BI32" s="21"/>
+      <c r="BJ32" s="21"/>
+      <c r="BK32" s="21"/>
+      <c r="BL32" s="21"/>
+      <c r="BM32" s="21"/>
+      <c r="BN32" s="21"/>
+      <c r="BO32" s="21"/>
+      <c r="BP32" s="21"/>
+      <c r="BQ32" s="21"/>
     </row>
-    <row r="33" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38">
-        <v>4.2</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41">
-        <v>0</v>
-      </c>
-      <c r="H33" s="42">
-        <v>0</v>
-      </c>
-      <c r="I33" s="52"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="54"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="54"/>
-      <c r="X33" s="54"/>
-      <c r="Y33" s="54"/>
-      <c r="Z33" s="54"/>
-      <c r="AA33" s="54"/>
-      <c r="AB33" s="54"/>
-      <c r="AC33" s="57"/>
-      <c r="AD33" s="57"/>
-      <c r="AE33" s="57"/>
-      <c r="AF33" s="57"/>
-      <c r="AG33" s="57"/>
-      <c r="AH33" s="54"/>
-      <c r="AI33" s="54"/>
-      <c r="AJ33" s="54"/>
-      <c r="AK33" s="54"/>
-      <c r="AL33" s="54"/>
-      <c r="AM33" s="54"/>
-      <c r="AN33" s="54"/>
-      <c r="AO33" s="54"/>
-      <c r="AP33" s="54"/>
-      <c r="AQ33" s="54"/>
-      <c r="AR33" s="58"/>
-      <c r="AS33" s="58"/>
-      <c r="AT33" s="58"/>
-      <c r="AU33" s="58"/>
-      <c r="AV33" s="58"/>
-      <c r="AW33" s="54"/>
-      <c r="AX33" s="54"/>
-      <c r="AY33" s="54"/>
-      <c r="AZ33" s="54"/>
-      <c r="BA33" s="54"/>
-      <c r="BB33" s="54"/>
-      <c r="BC33" s="54"/>
-      <c r="BD33" s="54"/>
-      <c r="BE33" s="54"/>
-      <c r="BF33" s="54"/>
-      <c r="BG33" s="59"/>
-      <c r="BH33" s="59"/>
-      <c r="BI33" s="59"/>
-      <c r="BJ33" s="59"/>
-      <c r="BK33" s="59"/>
-      <c r="BL33" s="54"/>
-      <c r="BM33" s="54"/>
-      <c r="BN33" s="54"/>
-      <c r="BO33" s="54"/>
-      <c r="BP33" s="60"/>
-      <c r="BQ33" s="37"/>
-    </row>
-    <row r="34" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38">
-        <v>4.3</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41">
-        <v>0</v>
-      </c>
-      <c r="H34" s="42">
-        <v>0</v>
-      </c>
-      <c r="I34" s="52"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="54"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="54"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="54"/>
-      <c r="X34" s="54"/>
-      <c r="Y34" s="54"/>
-      <c r="Z34" s="54"/>
-      <c r="AA34" s="54"/>
-      <c r="AB34" s="54"/>
-      <c r="AC34" s="57"/>
-      <c r="AD34" s="57"/>
-      <c r="AE34" s="57"/>
-      <c r="AF34" s="57"/>
-      <c r="AG34" s="57"/>
-      <c r="AH34" s="54"/>
-      <c r="AI34" s="54"/>
-      <c r="AJ34" s="54"/>
-      <c r="AK34" s="54"/>
-      <c r="AL34" s="54"/>
-      <c r="AM34" s="54"/>
-      <c r="AN34" s="54"/>
-      <c r="AO34" s="54"/>
-      <c r="AP34" s="54"/>
-      <c r="AQ34" s="54"/>
-      <c r="AR34" s="58"/>
-      <c r="AS34" s="58"/>
-      <c r="AT34" s="58"/>
-      <c r="AU34" s="58"/>
-      <c r="AV34" s="58"/>
-      <c r="AW34" s="54"/>
-      <c r="AX34" s="54"/>
-      <c r="AY34" s="54"/>
-      <c r="AZ34" s="54"/>
-      <c r="BA34" s="54"/>
-      <c r="BB34" s="54"/>
-      <c r="BC34" s="54"/>
-      <c r="BD34" s="54"/>
-      <c r="BE34" s="54"/>
-      <c r="BF34" s="54"/>
-      <c r="BG34" s="59"/>
-      <c r="BH34" s="59"/>
-      <c r="BI34" s="59"/>
-      <c r="BJ34" s="59"/>
-      <c r="BK34" s="59"/>
-      <c r="BL34" s="54"/>
-      <c r="BM34" s="54"/>
-      <c r="BN34" s="54"/>
-      <c r="BO34" s="54"/>
-      <c r="BP34" s="60"/>
-      <c r="BQ34" s="37"/>
-    </row>
-    <row r="35" spans="1:69" ht="17.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="41">
-        <v>0</v>
-      </c>
-      <c r="H35" s="61">
-        <v>0</v>
-      </c>
-      <c r="I35" s="52"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45"/>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45"/>
-      <c r="W35" s="54"/>
-      <c r="X35" s="54"/>
-      <c r="Y35" s="54"/>
-      <c r="Z35" s="54"/>
-      <c r="AA35" s="54"/>
-      <c r="AB35" s="54"/>
-      <c r="AC35" s="57"/>
-      <c r="AD35" s="57"/>
-      <c r="AE35" s="57"/>
-      <c r="AF35" s="57"/>
-      <c r="AG35" s="57"/>
-      <c r="AH35" s="54"/>
-      <c r="AI35" s="54"/>
-      <c r="AJ35" s="54"/>
-      <c r="AK35" s="54"/>
-      <c r="AL35" s="54"/>
-      <c r="AM35" s="54"/>
-      <c r="AN35" s="54"/>
-      <c r="AO35" s="54"/>
-      <c r="AP35" s="54"/>
-      <c r="AQ35" s="54"/>
-      <c r="AR35" s="58"/>
-      <c r="AS35" s="58"/>
-      <c r="AT35" s="58"/>
-      <c r="AU35" s="58"/>
-      <c r="AV35" s="58"/>
-      <c r="AW35" s="54"/>
-      <c r="AX35" s="54"/>
-      <c r="AY35" s="54"/>
-      <c r="AZ35" s="54"/>
-      <c r="BA35" s="54"/>
-      <c r="BB35" s="54"/>
-      <c r="BC35" s="54"/>
-      <c r="BD35" s="54"/>
-      <c r="BE35" s="54"/>
-      <c r="BF35" s="54"/>
-      <c r="BG35" s="59"/>
-      <c r="BH35" s="59"/>
-      <c r="BI35" s="59"/>
-      <c r="BJ35" s="59"/>
-      <c r="BK35" s="59"/>
-      <c r="BL35" s="54"/>
-      <c r="BM35" s="54"/>
-      <c r="BN35" s="54"/>
-      <c r="BO35" s="54"/>
-      <c r="BP35" s="60"/>
-      <c r="BQ35" s="37"/>
-    </row>
-    <row r="36" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
-      <c r="R36" s="21"/>
-      <c r="S36" s="21"/>
-      <c r="T36" s="21"/>
-      <c r="U36" s="21"/>
-      <c r="V36" s="21"/>
-      <c r="W36" s="21"/>
-      <c r="X36" s="21"/>
-      <c r="Y36" s="21"/>
-      <c r="Z36" s="21"/>
-      <c r="AA36" s="21"/>
-      <c r="AB36" s="21"/>
-      <c r="AC36" s="21"/>
-      <c r="AD36" s="21"/>
-      <c r="AE36" s="21"/>
-      <c r="AF36" s="21"/>
-      <c r="AG36" s="21"/>
-      <c r="AH36" s="21"/>
-      <c r="AI36" s="21"/>
-      <c r="AJ36" s="21"/>
-      <c r="AK36" s="21"/>
-      <c r="AL36" s="21"/>
-      <c r="AM36" s="21"/>
-      <c r="AN36" s="21"/>
-      <c r="AO36" s="21"/>
-      <c r="AP36" s="21"/>
-      <c r="AQ36" s="21"/>
-      <c r="AR36" s="21"/>
-      <c r="AS36" s="21"/>
-      <c r="AT36" s="21"/>
-      <c r="AU36" s="21"/>
-      <c r="AV36" s="21"/>
-      <c r="AW36" s="21"/>
-      <c r="AX36" s="21"/>
-      <c r="AY36" s="21"/>
-      <c r="AZ36" s="21"/>
-      <c r="BA36" s="21"/>
-      <c r="BB36" s="21"/>
-      <c r="BC36" s="21"/>
-      <c r="BD36" s="21"/>
-      <c r="BE36" s="21"/>
-      <c r="BF36" s="21"/>
-      <c r="BG36" s="21"/>
-      <c r="BH36" s="21"/>
-      <c r="BI36" s="21"/>
-      <c r="BJ36" s="21"/>
-      <c r="BK36" s="21"/>
-      <c r="BL36" s="21"/>
-      <c r="BM36" s="21"/>
-      <c r="BN36" s="21"/>
-      <c r="BO36" s="21"/>
-      <c r="BP36" s="21"/>
-      <c r="BQ36" s="21"/>
-    </row>
-    <row r="37" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
-      <c r="R37" s="21"/>
-      <c r="S37" s="21"/>
-      <c r="T37" s="21"/>
-      <c r="U37" s="21"/>
-      <c r="V37" s="21"/>
-      <c r="W37" s="21"/>
-      <c r="X37" s="21"/>
-      <c r="Y37" s="21"/>
-      <c r="Z37" s="21"/>
-      <c r="AA37" s="21"/>
-      <c r="AB37" s="21"/>
-      <c r="AC37" s="21"/>
-      <c r="AD37" s="21"/>
-      <c r="AE37" s="21"/>
-      <c r="AF37" s="21"/>
-      <c r="AG37" s="21"/>
-      <c r="AH37" s="21"/>
-      <c r="AI37" s="21"/>
-      <c r="AJ37" s="21"/>
-      <c r="AK37" s="21"/>
-      <c r="AL37" s="21"/>
-      <c r="AM37" s="21"/>
-      <c r="AN37" s="21"/>
-      <c r="AO37" s="21"/>
-      <c r="AP37" s="21"/>
-      <c r="AQ37" s="21"/>
-      <c r="AR37" s="21"/>
-      <c r="AS37" s="21"/>
-      <c r="AT37" s="21"/>
-      <c r="AU37" s="21"/>
-      <c r="AV37" s="21"/>
-      <c r="AW37" s="21"/>
-      <c r="AX37" s="21"/>
-      <c r="AY37" s="21"/>
-      <c r="AZ37" s="21"/>
-      <c r="BA37" s="21"/>
-      <c r="BB37" s="21"/>
-      <c r="BC37" s="21"/>
-      <c r="BD37" s="21"/>
-      <c r="BE37" s="21"/>
-      <c r="BF37" s="21"/>
-      <c r="BG37" s="21"/>
-      <c r="BH37" s="21"/>
-      <c r="BI37" s="21"/>
-      <c r="BJ37" s="21"/>
-      <c r="BK37" s="21"/>
-      <c r="BL37" s="21"/>
-      <c r="BM37" s="21"/>
-      <c r="BN37" s="21"/>
-      <c r="BO37" s="21"/>
-      <c r="BP37" s="21"/>
-      <c r="BQ37" s="21"/>
-    </row>
-    <row r="38" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="21"/>
-      <c r="R38" s="21"/>
-      <c r="S38" s="21"/>
-      <c r="T38" s="21"/>
-      <c r="U38" s="21"/>
-      <c r="V38" s="21"/>
-      <c r="W38" s="21"/>
-      <c r="X38" s="21"/>
-      <c r="Y38" s="21"/>
-      <c r="Z38" s="21"/>
-      <c r="AA38" s="21"/>
-      <c r="AB38" s="21"/>
-      <c r="AC38" s="21"/>
-      <c r="AD38" s="21"/>
-      <c r="AE38" s="21"/>
-      <c r="AF38" s="21"/>
-      <c r="AG38" s="21"/>
-      <c r="AH38" s="21"/>
-      <c r="AI38" s="21"/>
-      <c r="AJ38" s="21"/>
-      <c r="AK38" s="21"/>
-      <c r="AL38" s="21"/>
-      <c r="AM38" s="21"/>
-      <c r="AN38" s="21"/>
-      <c r="AO38" s="21"/>
-      <c r="AP38" s="21"/>
-      <c r="AQ38" s="21"/>
-      <c r="AR38" s="21"/>
-      <c r="AS38" s="21"/>
-      <c r="AT38" s="21"/>
-      <c r="AU38" s="21"/>
-      <c r="AV38" s="21"/>
-      <c r="AW38" s="21"/>
-      <c r="AX38" s="21"/>
-      <c r="AY38" s="21"/>
-      <c r="AZ38" s="21"/>
-      <c r="BA38" s="21"/>
-      <c r="BB38" s="21"/>
-      <c r="BC38" s="21"/>
-      <c r="BD38" s="21"/>
-      <c r="BE38" s="21"/>
-      <c r="BF38" s="21"/>
-      <c r="BG38" s="21"/>
-      <c r="BH38" s="21"/>
-      <c r="BI38" s="21"/>
-      <c r="BJ38" s="21"/>
-      <c r="BK38" s="21"/>
-      <c r="BL38" s="21"/>
-      <c r="BM38" s="21"/>
-      <c r="BN38" s="21"/>
-      <c r="BO38" s="21"/>
-      <c r="BP38" s="21"/>
-      <c r="BQ38" s="21"/>
+    <row r="33" spans="1:69" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="21"/>
+      <c r="W33" s="21"/>
+      <c r="X33" s="21"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="21"/>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="21"/>
+      <c r="AC33" s="21"/>
+      <c r="AD33" s="21"/>
+      <c r="AE33" s="21"/>
+      <c r="AF33" s="21"/>
+      <c r="AG33" s="21"/>
+      <c r="AH33" s="21"/>
+      <c r="AI33" s="21"/>
+      <c r="AJ33" s="21"/>
+      <c r="AK33" s="21"/>
+      <c r="AL33" s="21"/>
+      <c r="AM33" s="21"/>
+      <c r="AN33" s="21"/>
+      <c r="AO33" s="21"/>
+      <c r="AP33" s="21"/>
+      <c r="AQ33" s="21"/>
+      <c r="AR33" s="21"/>
+      <c r="AS33" s="21"/>
+      <c r="AT33" s="21"/>
+      <c r="AU33" s="21"/>
+      <c r="AV33" s="21"/>
+      <c r="AW33" s="21"/>
+      <c r="AX33" s="21"/>
+      <c r="AY33" s="21"/>
+      <c r="AZ33" s="21"/>
+      <c r="BA33" s="21"/>
+      <c r="BB33" s="21"/>
+      <c r="BC33" s="21"/>
+      <c r="BD33" s="21"/>
+      <c r="BE33" s="21"/>
+      <c r="BF33" s="21"/>
+      <c r="BG33" s="21"/>
+      <c r="BH33" s="21"/>
+      <c r="BI33" s="21"/>
+      <c r="BJ33" s="21"/>
+      <c r="BK33" s="21"/>
+      <c r="BL33" s="21"/>
+      <c r="BM33" s="21"/>
+      <c r="BN33" s="21"/>
+      <c r="BO33" s="21"/>
+      <c r="BP33" s="21"/>
+      <c r="BQ33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="P5:AA5"/>
+    <mergeCell ref="O2:AE2"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="P4:AB4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="BL9:BP9"/>
+    <mergeCell ref="BB9:BF9"/>
+    <mergeCell ref="BB8:BP8"/>
+    <mergeCell ref="AM9:AQ9"/>
+    <mergeCell ref="AM8:BA8"/>
+    <mergeCell ref="AR9:AV9"/>
+    <mergeCell ref="AW9:BA9"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="N9:R9"/>
+    <mergeCell ref="I9:M9"/>
+    <mergeCell ref="I8:W8"/>
+    <mergeCell ref="BG9:BK9"/>
+    <mergeCell ref="X8:AL8"/>
+    <mergeCell ref="X9:AB9"/>
+    <mergeCell ref="AH9:AL9"/>
+    <mergeCell ref="AC9:AG9"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="B8:B10"/>
@@ -4577,34 +4197,9 @@
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E10"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="N9:R9"/>
-    <mergeCell ref="I9:M9"/>
-    <mergeCell ref="I8:W8"/>
-    <mergeCell ref="BG9:BK9"/>
-    <mergeCell ref="BL9:BP9"/>
-    <mergeCell ref="BB9:BF9"/>
-    <mergeCell ref="BB8:BP8"/>
-    <mergeCell ref="AM9:AQ9"/>
-    <mergeCell ref="AM8:BA8"/>
-    <mergeCell ref="X8:AL8"/>
-    <mergeCell ref="X9:AB9"/>
-    <mergeCell ref="AH9:AL9"/>
-    <mergeCell ref="AC9:AG9"/>
-    <mergeCell ref="AR9:AV9"/>
-    <mergeCell ref="AW9:BA9"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="P5:AA5"/>
-    <mergeCell ref="O2:AE2"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="P4:AB4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H12:H18 H20:H35">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="H12:H18 H20:H30">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4612,7 +4207,7 @@
         <color rgb="FF57BB8A"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
